--- a/bin/Release/net8.0/Files/rajdhani-day-penal-chart.xlsx
+++ b/bin/Release/net8.0/Files/rajdhani-day-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$458</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$459</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -1432,12 +1432,6 @@
     <x:t>01/06/20 to 06/06/20</x:t>
   </x:si>
   <x:si>
-    <x:t>08/06/20tp16/06/20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
     <x:t>15/06/20 to 20/06/20</x:t>
   </x:si>
   <x:si>
@@ -1621,16 +1615,9 @@
     <x:t>09/08/21 to 14/08/21</x:t>
   </x:si>
   <x:si>
-    <x:t>16/08/21to21/08/2157022129256382606792313935970488599342391135516823/08/21to28/08/21278773596880114626865140469945903441277812.47956830/08/21to04/09/2157025258136036892709578033734590129251775601234506/09/21to11/09/2116747458390253391494716077829135234965562507312013/09/21to18/09/2134418288568902804464355026084167258551224701413020/09/21to25/09/2177931236230541301887023515731245379981703609426627/09/21to02/10/2156780136460092253564057814832480589242482350267904/10/21to09/10/2111685140990863584802358014509234355351771360789011/10/21to16/10/2136988990399136895702846826082390340771243373918018/10/21to23/10/2113043256345226884565712437777160357515792776515925/10/21to30/10/2114500370134891808806737728004149578021102585844001/11/21to06/11/21************************************************08/11/21to13/11/21********246278901247413035649199337383781584215615/11/21to20/11/2112587124236141671292512214830578268641496792266022/11/21to27/11/2115845447179792892259046059045690266436704598688029/11/21to04/12/2156012679780571795678322911244158779381701797727806/12/21to11/12/2112361236140541671225014546882390900911001461688013/12/21to18/12/2179061128133742571607468066793580123672693564444620/12/21to25/12/2125070569460036893306224658921335240641588996019027/12/21to01/01/2245655267700792342585330017865159589295682697756603/01/22to08/01/2217089379236126792462746724061245699416781203315710/01/22to15/01/2278949180489146802596569057027467450931485601655617/01/22to22/01/2215957890360941586994257056904400470167904565938824/01/22to29/01/222361013666912156********13827359160767906602134431/01/22to05/02/2257790280359774581595813424061119668024802608624007/02/22to12/02/2259047115158442571180844039028125800811461281124514/02/22to19/02/2235975366345271791674038915622336457643478907459021/02/22to26/02/2217973148224841306703737745092390490314701494056928/02/22to05/03/2289078189455423905803938828884680259681702406415807/03/22to12/03/2245879180126934456804234546668459129216784475817014/03/22to19/03/2234631245157326795500922557028170********7782813421/03/22to26/03/2235971470380126602260616948910127167462594408936028/03/22to02/04/2214504789134874584475249912928567670321562204616904/04/22to09/04/2256904338560122001562938828992345556671608996056911/04/22to16/04/2245985140468821561157516858031399560174491483923418/04/22to23/04/2224844130255285672462625936654239590431663889928925/04/22to30/04/2268048567569091262002046017087188468864571775167802/05/22to07/05/2256787359366563674701378824627557699491351696212909/05/22to14/05/228895414959047133********18985267227141301360514016/05/22to21/05/2226759225124704884992717912705357134815601674013623/05/22to28/05/2211919135124784594699122711573490380114893463515930/05/22to04/06/2236988134245161696006033447011137159522551797028006/06/22to11/06/2224624167788341493362147022606169158433461786220013/06/22to18/06/2245098170359711198895516868821560266426791292367020/06/20to26/06/2213608378356426884666013625969900479074675599912627/06/22to02/07/2215624167266415604565029912361236299042393890914404/07/22to09/07/2245982345340774672888312015730244137115601786633011/07/22to16/07/2214050460345242578806579939915456268622463306550018/07/22to23/07/2212928134334071793597726915844338110261695904234525/07/22to30/07/2246005159799505699908215645094446160778904802445501/08/22to06/08/2256905168146131571191624044978189468831661573249908/08/22to13/08/2246775168245132473991827947908990780553481775110015/08/22to20/08/22********135931483395334636877223247361691135746722/08/22to27/08/2236981560350855002552514068043247356473401506367029/08/22to03/09/2222592237120362402451735924954112477802351360123605/09/22to10/09/2211024356669121291584956857808125250731203575422012/09/22to17/09/2214617278488016786905066826752570149495687704550019/09/22to24/09/2226084680567836704666129056019379380134451472411226/09/22to01/10/2214830190249571608907517788952480460033005702435603/10/22to08/10/2215733580458723364802038922041489478923452002770010/10/22to15/10/2235644158168531397906534856679135479042664802836917/10/22to22/10/226691626812472156180953394802936018980389********24/10/22to29/10/22************************************************31/10/22to05/11/2213596790780582606893344515950460227162591382358007/11/22to12/11/2211914149248462595678536645980145448605693609660014/11/22to19/11/2224958369190062403373478911463779138214895993526721/11/22to26/11/2234744356268616692800114623052246579161693340745828/11/22to03/12/2224843445135942573700735944755230468801902350359905/12/22to10/12/2238012345567863671180316612583157200274676804133512/12/22to17/12/2289072390119134455892826068937179370093604497459019/12/22to24/12/2228008189250702266792312068829568470168803373836926/12/22to31/12/2256785249234911003441257022041245450982791483110002/01/23to07/01/2346998170150602805566478915623779130431575601138009/01/23to14/01/232787416770078134360984402338624014501146601349016/01/23to21/01/2358922390179783502608923466022156244046803452737723/01/23to28/01/23890751403407349023619379********900915883597813430/01/23to04/02/2334740668459863305791147024069469350842573788918006/02/23to11/02/2367037359169691356691033424515168339572693597212913/02/23to18/02/2344086556460025706905239057805230236132563340156020/02/23to25/02/2378945159469953571124624028000136129215881258913527/02/23to04/03/2345092138668092701236415818987269489122371146014506/03/23to11/03/231461578035641560********69053337137106683799634913/03/23to18/03/2368932138900991351595024447905249688234901584569020/03/23to25/03/2334412570156261694565312099087467157341495780316627/03/23to01/04/2357027458177503701359359956784158378811376691435603/04/23to08/04/2325639568340751132990019014505168356405696804735910/04/23to15/04/2355883490120373402394012744971155236163582473334617/04/23to22/04/2316965249168503343351267915952345677015882709936024/04/23to29/04/2313045780350891802484315767034347135972697894813401/05/23to06/05/2322480460227131482563315723058440128171602990066808/05/23to13/05/2315733490469946991472012713934149136012454408047915/05/23to20/05/2345097133249554563597133523380578156223459908334622/05/23to27/05/2323941579359712903452248047908990128152304891836929/05/23to03/06/2316635159136072695702138039028189280043561607067705/06/23to10/06/2323499667460031571359734024404789257421291179646612/06/23to17/06/2329016150235063495779459024737557190023901449912619/06/23to24/06/2316742147680494698996014526088567349616691281612326/06/23to01/07/2356013120360971151304267923831489166315883586736803/07/23to08/07/2348808378370072501506014527097160119194693340826010/07/23to15/07/2346990479568981342664611424848260480252583609214717/07/23to22/07/2315735690268601451225167849035500267592703801523024/07/23to29/07/2345987269134893602451626812478125556631392293123631/07/23to05/08/2339028567580362592338947845659289360941303700037007/08/23to12/08/2323948800268622465678734023386178115736709908478914/08/23to19/08/2357802138********6703067755009126248491356905578021/08/23to26/08/2326972138447501363306424846994130260812454464523028/08/23to02/09/2349034112460032565803212999082228159574581102239004/09/23to09/09/2313041380133772501584918068935168228231482349358011/09/23to17/09/2313607467167491994509938846770479155156902462923418/09/23to23/09/2366807160140553392675147040040190137173595500157925/09/23to30/09/2318097467244082882350515923834112168501901461424802/10/23to07/10/2334079450118051681898422012036169470171601337215609/10/23to14/10/2349036268479071795588223726759568360902802349156016/10/23to21/10/2312254239890751132608611447907359678183781371012723/10/23to28/10/2338904356360981161393534823831137589231571102425730/10/23to04/11/2337007368128141502664123623946150129222371360134406/11/23to11/11/2357912589600683784600844079064338****************13/11/23to18/11/23************************************************20/11/23to25/11/2322606349123631482901157945986240257413441674067727/11/23to02/12/2323509379234943472686679013824158478974671898022604/12/23to09/12/2334633689178641493441636724515456379911281775918011/12/23to16/12/2325746178169633375993945056907124167483502507956818/12/23to23/12/2337997160127027781269414935866150390271791180335625/12/23to30/12/2313714239189871157805918090092390124753661371133501/01/24to06/01/2412923148135991261797047938905339246216781359908/01/24to13/01/2425526123790643471180835025850479180995774475028015/01/24to20/01/2467816790489171881797046013483580770403893609138022/01/24to27/01/2479063355680451401506214790095168********5702134429/01/24to03/02/2424733148680462681584413045760479677024802686224605/02/24to10/02/2412696358448678901258847736981380127023453553112812/02/24to17/02/2414944356679231484464735945764455580312363687066819/02/24to24/02/2447908459259662402787855814503599577935801270056926/02/24to02/03/2428993120500573683801956858813256360961785702822404/03/24to09/03/2430034220269732474992368924628369257416783698423911/03/24to16/03/2413371236340775572002818914942679359763498008945018/03/24to23/03/2428995168123661148806112826080190145054561168325625/03/24to30/03/24********590451401225826066913166236104791900789001/04/24to06/04/2414941245689333001360927068041146136031391663828808/04/24to13/04/2428999568460081894453726934968369170816691461122715/04/24to20/04/2424063689300371792798258912706457380156901551616922/04/24to27/04/2446775113449725703575349012584680226052302293367029/04/24to04/05/2426756457136026791168817035759126660221383362434706/05/24to12/05/2412812138389051404701423944861146125802991898057813/05/24to16/05/2457919379330653481494033448914167790672694778038920/05/24to25/05/2412816178189832381157157934074590468842201102215627/05/24to01/06/2423615230790636705599734058033247180951771225434703/06/24to08/06/2449031560579184405702248024628260279872237007615010/06/24to15/06/2449030235680482604475166945982110489152676691616917/06/24to22/06/2417971470250791806905514026081489224831578008416724/06/24to29/06/2458033256158464481236459024063247668089904802927001/07/24to06/07/2448919469236131391562919978056123179751595577947808/07/24to13/07/2425968468113532381595713358814248468812904802645715/07/24to20/07/2458030550579145903395414948912156356404792338257022/07/24to28/07/2445870370348545902888525815841678340744465702946929/07/24to03/08/2445763580250794694598811677044149280023903395736805/08/24to10/08/2457026448380183505678937930038468136071793777735912/08/24to17/08/24146103705791837856904248********280012904666957719/08/24to24/08/2423940370369823455780578014725159233861503801912626/08/24to31/08/2456011290257491806679725035977160556642392507167802/09/2024to07/09/202489969234348511007906124518870550126915793441835009/09/24to14/09/2415959469677041581494129045652688468883692899426616/09/24to21/09/2444642156379967901775157958923445550091351405826023/09/24to28/09/2455669135280052673890534825740136790615881102535730/09/24to05/10/2427091137136035803508239066029559148374496882148907/10/24to12/10/2456781137340774581371028014052390119102353597478914/10/24to19/10/2459042246344163304509946968042570159512457805416721/10/24to26/10/2446662390280061237793037023832570350804882709138028/10/24to02/11/24************************************************04/11/24to09/11/24****************4677919945098459278732474699223711/11/24to16/11/2411806259579102801887424878948134600662681573846818/11/24to23/11/2416743148579194503687818933515140270933004004818925/11/24to30/11/2436877160580384592383239035863346679245903801330002/12/24to07/12/2437005357990852677894435647907557466602356804234509/12/24to14/12/2466791470120373771573147013826150336251681348114616/12/24to21/12/2467810235123641302451012712476240135924992664012723/12/2024to28/12/202445766259235091441809435636095177135902802697550030/12/24to04/01/2567811236770405693575214749039559146101362204545606/01/25to11/01/2578059360136051684701459025741588229354564576635813/01/25to18/01/2513719117139383691102946924842390160782795690579920/01/25to25/01/2558039478556664661786414957020190477862593395358027/01/25to01/02/2515063148137116693575023518982200800823901292569003/02/25to08/02/2555663346127001904701459034070578388913351584037010/02/25to15/02/2522487359235094694565411255883670168513805690517717/02/25to22/02/2524067359146121562608727827769126477874582585066824/02/25to01/03/2526865690256331481135046013599270269752583801224603/03/25to08/03/2515952688117973681203534848808350789467903373324710/03/25to15/03/2537883157334051771382212936878477********3597148917/03/25to22/03/2534965113119133553452947913717124135981251203578024/03/25to29/03/2518096367357521101449019034964149339513445702913531/03/25to05/04/2559040460345278904701579977046466270994501696046007/04/25to12/04/2516073490167491172473367035649379125833461999624014/04/25to19/04/2523505230469973404790257046774167149403899908167821/04/25to26/04/2513937250339501272800822425855177120316694600223728/04/25to03/05/2547896240169652492293248047015690490331396691224605/05/25to10/05/2530030190180942482495213844860280678163491179156012/05/25to17/05/252608067779959117120378905667235670341492901333719/05/25to24/05/2523490127238371602675029926646240168501901449444626/05/25to31/05/2534740389249546802709516824069450466661508907689902/06/25to07/06/2557914167247361691461718825963238590412455702268809/06/25to14/06/2556907250110271603801846867036880340781251663945016/06/25to21/06/2523720145248416783890856749920145379981341203314823/06/25to28/06/2568041588134836704903736845097250469912362574727830/06/25to05/07/2568040389458771605702335511246150779302356882414907/07/25to12/07/2512920127580372781359533927989270227122373003936014/07/25to19/07/253474537345211463003215612478477159515603496578021/07/2025to26/07/202570074149150663581562836977043670256394694701335528/07/25to02/08/2526087700468811465577717916854680147201905791112804/08/25to09/08/252383569055779900308213846885456448627783407110011/08/25to16/08/2523490460169684401269523033067467********1348626818/08/25to23/08/2546008279170821292406535714721380239433465791928925/08/25to30/08/2546884167166371791360534822480334146113801348569001/09/25to06/09/2545094590250732293597440015511678290147701304257008/09/25to13/09/2523729234450973402361937933061146180981344565745815/09/25to20/09/2557026169136042571371047935648224113562403700033422/09/25to26/09/2516967458240616784497367013375357789415605689413029/09/25to04/10/2513483238778211285892349016967124449702266703019006/10/25to11/10/2512366457156278902350636727095690600674492259046013/10/2025to18/10/20251450847734969360668062594802425735971678********20/10/25to25/10/25************************************************27/10/25to01/11/2518981399367672502350535722378125138222378996413003/11/25to08/11/2568044188558861235702220036870235190095681359333710/11/25to15/11/2528008350129271151382258911914590150631574790523017/11/25to22/11/2523834149449724802282615024514248135972693799755724/11/25to29/11/2515620479770491802462746734850136138203701809689901/12/25to06/12/2517084167680443563801517768822110880673681607545608/12/25to13/12/2517970479237296671179129035757557177521563441745815/12/25to20/12/251797070358684406602459016631669350844553687718822/12/25to28/12/252875780680442484891625923492237899605784576946929/11/25to03/01/2619001560136063585702579923380370345232563890147005/01/2026to10/01/202612699360368792702394837847900578367641302372029912/01/2026to18/01/202623494789233871243902634945988224356471881360837819/01/2026to24/01/202611460389469989901258249957023580118013803575837826/01/2026to31/01/2026********117994502798138033513238799552301461248002/02/2026to07/02/202666800460119151681708413013040460456594784464315709/02/2026to14/02/202645095140500572234789223727875447460031574408224616/02/2026to21/02/202616079360455446801696046037001399146191266703048823/02/2026to28/02/202638014347556601452675322956010280668012907894856702/03/2026to07/03/20266703817027761560********48917269889573776905312009/03/2026To14/03/202614504220149421381304927023838990337321564891013616/03/2026to21/03/202635642570500512454802835013592138278736701337377923/03/2026to28/03/202648024347269711551685019011351470550015792901239030/03/2026to04/04/202613486448889543383508257016967890157326881135912606/04/2026to11/04/202625071678570271791179333713595690557793604509856713/04/2026to19/04/202647902480556668807906837818090190134884778907316620/04/2026to25/04/202655991579345273686905636778050235127066002697812527/04/2026to02/05/202644751344234905698895744947895780590414702372038904/05/2026to09/05/202619993247450924804600644889966240790684401281435611/05/2026to16/05/202645872228249505783575213834969379350813801900535718/05/2026to21/05/202614500136890799006994138060065258160723901405414925/05/2026to30/05/202617861560670314897704817059045159579173404992066801/06/2026to06/06/202625969270236102801551617823051470599341673698277808/06/2026to13/06/202658036169467704602248633012581146100131202901511315/06/2026to20/06/202634969126159557801696770019999469167442572776224622/06/2026to27/06/202612927890390254561900037028995500150646804475023529/06/2026to04/07/202634966358688202805904258967925357245103894891257006/07/2026to11/07/202611359135100144551382644868937340370061238806330013/07/2026to18/07/202636988378370071334600826046775177900982792507012720/07/2026to25/07/202613604680118044003902817014503455188741492440937927/07/2026to01/08/20266893923415958800677014702608046023386150270991503/08/2026to08/08/202634638260147295773575526725743256266446803003028010/08/2026to15/08/20261898422012363120136082602495726916850569********17/08/2026to22/08/202633848125356468807883625945982129Go to TopRAJDHANI DAY459-82-129Refresh Resultअब सभी मटका बाजार खेलो ऑनलाइन ऐप पररोज खेलो रोज कमाओ अभी डाउनलोड करो👉 Online Matka Play(Direct)~ Kalyan Official App ~Super Fast deposit and withdrawal[ 卐 बुकिंग चालू | बुकिंग चालू 卐  ]कल्याण बाजार बम्पर धमाका अचूक जोड़ी पर कमाओ लाखों 100% फिक्स 1 जोड़ी 2 पत्ती सिर्फ एक दिन में-पूरा लॉस कबर होगा मनी बैक गारंटी
-एडवांस चार्ज 2500/- मात्रकॉल : 08829959562कॉल : 08829959562Note :-Don't Call For Trail HelpThe Rajdhani Day Panel Chart on SattaMatkaDpboss.Mobi is one of the most complete chart archives available online for the Rajdhani Day Matka market. Players who study the Rajdhani Day Panel Chart regularly can identify hot panna numbers, spot recurring three-digit combinations, and track open close digit patterns across weeks and months. This chart goes back to 2017 and is updated daily after every result declaration — completely free with no registration required.The Rajdhani Day Panel Chart is available in several forms including Rajdhani Day Panel Chart 2011, Rajdhani Day Panel Chart 2012, Rajdhani Day Panel Chart 2013, Rajdhani Day Panel Chart 2014, Rajdhani Day Panel Chart 2016, and the most current Rajdhani Day Panel Chart record. Each version helps players study historical trends across different time periods for deeper number analysis. At SattaMatkaDpboss.Mobi we keep updating the Rajdhani Day Panel Chart with new results continuously making it one of the most valuable tools for improving overall strategy in the Rajdhani Day market.Join our WhatsApp channel for fast ResultHome|Matka Guessing|Matka Chart|Matka Play|Tara Matka|Fix Matka|SitemapSattaMatkaDpboss.MobiALL RIGHTS RESERVED (2012-2026)SITE OWNER:-PRO. BIG BOSS SIR08829959562https://sattamatkadpboss.mobi</x:t>
-  </x:si>
-  <x:si>
     <x:t>23/08/21 to 28/08/21</x:t>
   </x:si>
   <x:si>
-    <x:t>12.4</x:t>
-  </x:si>
-  <x:si>
     <x:t>30/08/21 to 04/09/21</x:t>
   </x:si>
   <x:si>
@@ -2409,6 +2396,9 @@
   </x:si>
   <x:si>
     <x:t>17/08/2026 to 22/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/08/2026 to 29/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2540,7 +2530,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -2555,10 +2545,6 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2868,7 +2854,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V458"/>
+  <x:dimension ref="A1:V459"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -12114,18 +12100,18 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="T136" s="3" t="s">
-        <x:v>471</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U136" s="3" t="s">
-        <x:v>168</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V136" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:22">
       <x:c r="A137" s="3" t="s">
-        <x:v>473</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B137" s="3" t="s">
         <x:v>159</x:v>
@@ -12193,7 +12179,7 @@
     </x:row>
     <x:row r="138" spans="1:22">
       <x:c r="A138" s="3" t="s">
-        <x:v>474</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B138" s="3" t="s">
         <x:v>105</x:v>
@@ -12261,7 +12247,7 @@
     </x:row>
     <x:row r="139" spans="1:22">
       <x:c r="A139" s="3" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B139" s="3" t="s">
         <x:v>62</x:v>
@@ -12329,7 +12315,7 @@
     </x:row>
     <x:row r="140" spans="1:22">
       <x:c r="A140" s="3" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B140" s="3" t="s">
         <x:v>193</x:v>
@@ -12397,7 +12383,7 @@
     </x:row>
     <x:row r="141" spans="1:22">
       <x:c r="A141" s="3" t="s">
-        <x:v>477</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B141" s="3" t="s">
         <x:v>140</x:v>
@@ -12465,7 +12451,7 @@
     </x:row>
     <x:row r="142" spans="1:22">
       <x:c r="A142" s="3" t="s">
-        <x:v>478</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B142" s="3" t="s">
         <x:v>113</x:v>
@@ -12533,7 +12519,7 @@
     </x:row>
     <x:row r="143" spans="1:22">
       <x:c r="A143" s="3" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B143" s="3" t="s">
         <x:v>200</x:v>
@@ -12601,7 +12587,7 @@
     </x:row>
     <x:row r="144" spans="1:22">
       <x:c r="A144" s="3" t="s">
-        <x:v>480</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B144" s="3" t="s">
         <x:v>68</x:v>
@@ -12669,7 +12655,7 @@
     </x:row>
     <x:row r="145" spans="1:22">
       <x:c r="A145" s="3" t="s">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B145" s="3" t="s">
         <x:v>312</x:v>
@@ -12737,7 +12723,7 @@
     </x:row>
     <x:row r="146" spans="1:22">
       <x:c r="A146" s="3" t="s">
-        <x:v>482</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B146" s="3" t="s">
         <x:v>229</x:v>
@@ -12805,7 +12791,7 @@
     </x:row>
     <x:row r="147" spans="1:22">
       <x:c r="A147" s="3" t="s">
-        <x:v>483</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B147" s="3" t="s">
         <x:v>79</x:v>
@@ -12873,7 +12859,7 @@
     </x:row>
     <x:row r="148" spans="1:22">
       <x:c r="A148" s="3" t="s">
-        <x:v>484</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B148" s="3" t="s">
         <x:v>389</x:v>
@@ -12941,7 +12927,7 @@
     </x:row>
     <x:row r="149" spans="1:22">
       <x:c r="A149" s="3" t="s">
-        <x:v>485</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B149" s="3" t="s">
         <x:v>292</x:v>
@@ -13009,7 +12995,7 @@
     </x:row>
     <x:row r="150" spans="1:22">
       <x:c r="A150" s="3" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B150" s="3" t="s">
         <x:v>290</x:v>
@@ -13077,7 +13063,7 @@
     </x:row>
     <x:row r="151" spans="1:22">
       <x:c r="A151" s="3" t="s">
-        <x:v>487</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B151" s="3" t="s">
         <x:v>56</x:v>
@@ -13145,7 +13131,7 @@
     </x:row>
     <x:row r="152" spans="1:22">
       <x:c r="A152" s="3" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B152" s="3" t="s">
         <x:v>332</x:v>
@@ -13213,7 +13199,7 @@
     </x:row>
     <x:row r="153" spans="1:22">
       <x:c r="A153" s="3" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B153" s="3" t="s">
         <x:v>259</x:v>
@@ -13281,7 +13267,7 @@
     </x:row>
     <x:row r="154" spans="1:22">
       <x:c r="A154" s="3" t="s">
-        <x:v>490</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B154" s="3" t="s">
         <x:v>23</x:v>
@@ -13349,7 +13335,7 @@
     </x:row>
     <x:row r="155" spans="1:22">
       <x:c r="A155" s="3" t="s">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B155" s="3" t="s">
         <x:v>150</x:v>
@@ -13417,7 +13403,7 @@
     </x:row>
     <x:row r="156" spans="1:22">
       <x:c r="A156" s="3" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B156" s="3" t="s">
         <x:v>37</x:v>
@@ -13485,7 +13471,7 @@
     </x:row>
     <x:row r="157" spans="1:22">
       <x:c r="A157" s="3" t="s">
-        <x:v>493</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B157" s="3" t="s">
         <x:v>101</x:v>
@@ -13553,7 +13539,7 @@
     </x:row>
     <x:row r="158" spans="1:22">
       <x:c r="A158" s="3" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B158" s="3" t="s">
         <x:v>201</x:v>
@@ -13621,7 +13607,7 @@
     </x:row>
     <x:row r="159" spans="1:22">
       <x:c r="A159" s="3" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B159" s="3" t="s">
         <x:v>229</x:v>
@@ -13689,7 +13675,7 @@
     </x:row>
     <x:row r="160" spans="1:22">
       <x:c r="A160" s="3" t="s">
-        <x:v>496</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B160" s="3" t="s">
         <x:v>295</x:v>
@@ -13757,7 +13743,7 @@
     </x:row>
     <x:row r="161" spans="1:22">
       <x:c r="A161" s="3" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B161" s="3" t="s">
         <x:v>95</x:v>
@@ -13825,7 +13811,7 @@
     </x:row>
     <x:row r="162" spans="1:22">
       <x:c r="A162" s="3" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B162" s="3" t="s">
         <x:v>281</x:v>
@@ -13893,7 +13879,7 @@
     </x:row>
     <x:row r="163" spans="1:22">
       <x:c r="A163" s="3" t="s">
-        <x:v>499</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B163" s="3" t="s">
         <x:v>46</x:v>
@@ -13961,7 +13947,7 @@
     </x:row>
     <x:row r="164" spans="1:22">
       <x:c r="A164" s="3" t="s">
-        <x:v>500</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B164" s="3" t="s">
         <x:v>375</x:v>
@@ -14029,7 +14015,7 @@
     </x:row>
     <x:row r="165" spans="1:22">
       <x:c r="A165" s="3" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B165" s="3" t="s">
         <x:v>200</x:v>
@@ -14097,7 +14083,7 @@
     </x:row>
     <x:row r="166" spans="1:22">
       <x:c r="A166" s="3" t="s">
-        <x:v>502</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B166" s="3" t="s">
         <x:v>65</x:v>
@@ -14165,7 +14151,7 @@
     </x:row>
     <x:row r="167" spans="1:22">
       <x:c r="A167" s="3" t="s">
-        <x:v>503</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B167" s="3" t="s">
         <x:v>320</x:v>
@@ -14233,7 +14219,7 @@
     </x:row>
     <x:row r="168" spans="1:22">
       <x:c r="A168" s="3" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B168" s="3" t="s">
         <x:v>40</x:v>
@@ -14301,7 +14287,7 @@
     </x:row>
     <x:row r="169" spans="1:22">
       <x:c r="A169" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B169" s="3" t="s">
         <x:v>133</x:v>
@@ -14369,7 +14355,7 @@
     </x:row>
     <x:row r="170" spans="1:22">
       <x:c r="A170" s="3" t="s">
-        <x:v>506</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B170" s="3" t="s">
         <x:v>79</x:v>
@@ -14437,7 +14423,7 @@
     </x:row>
     <x:row r="171" spans="1:22">
       <x:c r="A171" s="3" t="s">
-        <x:v>507</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B171" s="3" t="s">
         <x:v>184</x:v>
@@ -14505,7 +14491,7 @@
     </x:row>
     <x:row r="172" spans="1:22">
       <x:c r="A172" s="3" t="s">
-        <x:v>508</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B172" s="3" t="s">
         <x:v>266</x:v>
@@ -14573,7 +14559,7 @@
     </x:row>
     <x:row r="173" spans="1:22">
       <x:c r="A173" s="3" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B173" s="3" t="s">
         <x:v>94</x:v>
@@ -14641,7 +14627,7 @@
     </x:row>
     <x:row r="174" spans="1:22">
       <x:c r="A174" s="3" t="s">
-        <x:v>510</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B174" s="3" t="s">
         <x:v>191</x:v>
@@ -14709,7 +14695,7 @@
     </x:row>
     <x:row r="175" spans="1:22">
       <x:c r="A175" s="3" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B175" s="3" t="s">
         <x:v>115</x:v>
@@ -14777,7 +14763,7 @@
     </x:row>
     <x:row r="176" spans="1:22">
       <x:c r="A176" s="3" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B176" s="3" t="s">
         <x:v>165</x:v>
@@ -14845,7 +14831,7 @@
     </x:row>
     <x:row r="177" spans="1:22">
       <x:c r="A177" s="3" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B177" s="3" t="s">
         <x:v>34</x:v>
@@ -14913,7 +14899,7 @@
     </x:row>
     <x:row r="178" spans="1:22">
       <x:c r="A178" s="3" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B178" s="3" t="s">
         <x:v>201</x:v>
@@ -14981,7 +14967,7 @@
     </x:row>
     <x:row r="179" spans="1:22">
       <x:c r="A179" s="3" t="s">
-        <x:v>515</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B179" s="3" t="s">
         <x:v>191</x:v>
@@ -15049,7 +15035,7 @@
     </x:row>
     <x:row r="180" spans="1:22">
       <x:c r="A180" s="3" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B180" s="3" t="s">
         <x:v>195</x:v>
@@ -15117,7 +15103,7 @@
     </x:row>
     <x:row r="181" spans="1:22">
       <x:c r="A181" s="3" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B181" s="3" t="s">
         <x:v>65</x:v>
@@ -15185,7 +15171,7 @@
     </x:row>
     <x:row r="182" spans="1:22">
       <x:c r="A182" s="3" t="s">
-        <x:v>518</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B182" s="3" t="s">
         <x:v>99</x:v>
@@ -15253,7 +15239,7 @@
     </x:row>
     <x:row r="183" spans="1:22">
       <x:c r="A183" s="3" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B183" s="3" t="s">
         <x:v>91</x:v>
@@ -15321,7 +15307,7 @@
     </x:row>
     <x:row r="184" spans="1:22">
       <x:c r="A184" s="3" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B184" s="3" t="s">
         <x:v>406</x:v>
@@ -15389,7 +15375,7 @@
     </x:row>
     <x:row r="185" spans="1:22">
       <x:c r="A185" s="3" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B185" s="3" t="s">
         <x:v>174</x:v>
@@ -15457,7 +15443,7 @@
     </x:row>
     <x:row r="186" spans="1:22">
       <x:c r="A186" s="3" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B186" s="3" t="s">
         <x:v>149</x:v>
@@ -15525,7 +15511,7 @@
     </x:row>
     <x:row r="187" spans="1:22">
       <x:c r="A187" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B187" s="3" t="s">
         <x:v>304</x:v>
@@ -15593,7 +15579,7 @@
     </x:row>
     <x:row r="188" spans="1:22">
       <x:c r="A188" s="3" t="s">
-        <x:v>524</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B188" s="3" t="s">
         <x:v>229</x:v>
@@ -15661,7 +15647,7 @@
     </x:row>
     <x:row r="189" spans="1:22">
       <x:c r="A189" s="3" t="s">
-        <x:v>525</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B189" s="3" t="s">
         <x:v>275</x:v>
@@ -15729,7 +15715,7 @@
     </x:row>
     <x:row r="190" spans="1:22">
       <x:c r="A190" s="3" t="s">
-        <x:v>526</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B190" s="3" t="s">
         <x:v>51</x:v>
@@ -15797,7 +15783,7 @@
     </x:row>
     <x:row r="191" spans="1:22">
       <x:c r="A191" s="3" t="s">
-        <x:v>527</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B191" s="3" t="s">
         <x:v>281</x:v>
@@ -15865,7 +15851,7 @@
     </x:row>
     <x:row r="192" spans="1:22">
       <x:c r="A192" s="3" t="s">
-        <x:v>528</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B192" s="3" t="s">
         <x:v>69</x:v>
@@ -15933,7 +15919,7 @@
     </x:row>
     <x:row r="193" spans="1:22">
       <x:c r="A193" s="3" t="s">
-        <x:v>529</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B193" s="3" t="s">
         <x:v>110</x:v>
@@ -16001,7 +15987,7 @@
     </x:row>
     <x:row r="194" spans="1:22">
       <x:c r="A194" s="3" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B194" s="3" t="s">
         <x:v>270</x:v>
@@ -16069,7 +16055,7 @@
     </x:row>
     <x:row r="195" spans="1:22">
       <x:c r="A195" s="3" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B195" s="3" t="s">
         <x:v>328</x:v>
@@ -16137,7 +16123,7 @@
     </x:row>
     <x:row r="196" spans="1:22">
       <x:c r="A196" s="3" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B196" s="3" t="s">
         <x:v>104</x:v>
@@ -16205,7 +16191,7 @@
     </x:row>
     <x:row r="197" spans="1:22">
       <x:c r="A197" s="3" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B197" s="3" t="s">
         <x:v>291</x:v>
@@ -16261,19 +16247,19 @@
       <x:c r="S197" s="3" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="T197" s="4" t="s">
-        <x:v>534</x:v>
+      <x:c r="T197" s="3" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="U197" s="3" t="s">
-        <x:v>316</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="V197" s="3" t="s">
-        <x:v>472</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:22">
       <x:c r="A198" s="3" t="s">
-        <x:v>535</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B198" s="3" t="s">
         <x:v>111</x:v>
@@ -16321,7 +16307,7 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="Q198" s="3" t="s">
-        <x:v>536</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="R198" s="3" t="s">
         <x:v>129</x:v>
@@ -16341,7 +16327,7 @@
     </x:row>
     <x:row r="199" spans="1:22">
       <x:c r="A199" s="3" t="s">
-        <x:v>537</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B199" s="3" t="s">
         <x:v>295</x:v>
@@ -16409,7 +16395,7 @@
     </x:row>
     <x:row r="200" spans="1:22">
       <x:c r="A200" s="3" t="s">
-        <x:v>538</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B200" s="3" t="s">
         <x:v>57</x:v>
@@ -16477,7 +16463,7 @@
     </x:row>
     <x:row r="201" spans="1:22">
       <x:c r="A201" s="3" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B201" s="3" t="s">
         <x:v>360</x:v>
@@ -16545,7 +16531,7 @@
     </x:row>
     <x:row r="202" spans="1:22">
       <x:c r="A202" s="3" t="s">
-        <x:v>540</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B202" s="3" t="s">
         <x:v>282</x:v>
@@ -16613,7 +16599,7 @@
     </x:row>
     <x:row r="203" spans="1:22">
       <x:c r="A203" s="3" t="s">
-        <x:v>541</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B203" s="3" t="s">
         <x:v>99</x:v>
@@ -16681,7 +16667,7 @@
     </x:row>
     <x:row r="204" spans="1:22">
       <x:c r="A204" s="3" t="s">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B204" s="3" t="s">
         <x:v>381</x:v>
@@ -16749,7 +16735,7 @@
     </x:row>
     <x:row r="205" spans="1:22">
       <x:c r="A205" s="3" t="s">
-        <x:v>543</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B205" s="3" t="s">
         <x:v>169</x:v>
@@ -16817,7 +16803,7 @@
     </x:row>
     <x:row r="206" spans="1:22">
       <x:c r="A206" s="3" t="s">
-        <x:v>544</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B206" s="3" t="s">
         <x:v>101</x:v>
@@ -16885,7 +16871,7 @@
     </x:row>
     <x:row r="207" spans="1:22">
       <x:c r="A207" s="3" t="s">
-        <x:v>545</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B207" s="3" t="s">
         <x:v>226</x:v>
@@ -16953,7 +16939,7 @@
     </x:row>
     <x:row r="208" spans="1:22">
       <x:c r="A208" s="3" t="s">
-        <x:v>546</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B208" s="3" t="s">
         <x:v>201</x:v>
@@ -17021,7 +17007,7 @@
     </x:row>
     <x:row r="209" spans="1:22">
       <x:c r="A209" s="3" t="s">
-        <x:v>547</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B209" s="3" t="s">
         <x:v>201</x:v>
@@ -17089,7 +17075,7 @@
     </x:row>
     <x:row r="210" spans="1:22">
       <x:c r="A210" s="3" t="s">
-        <x:v>548</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B210" s="3" t="s">
         <x:v>50</x:v>
@@ -17157,7 +17143,7 @@
     </x:row>
     <x:row r="211" spans="1:22">
       <x:c r="A211" s="3" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B211" s="3" t="s">
         <x:v>205</x:v>
@@ -17225,7 +17211,7 @@
     </x:row>
     <x:row r="212" spans="1:22">
       <x:c r="A212" s="3" t="s">
-        <x:v>550</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B212" s="3" t="s">
         <x:v>51</x:v>
@@ -17293,7 +17279,7 @@
     </x:row>
     <x:row r="213" spans="1:22">
       <x:c r="A213" s="3" t="s">
-        <x:v>551</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B213" s="3" t="s">
         <x:v>256</x:v>
@@ -17361,7 +17347,7 @@
     </x:row>
     <x:row r="214" spans="1:22">
       <x:c r="A214" s="3" t="s">
-        <x:v>552</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B214" s="3" t="s">
         <x:v>79</x:v>
@@ -17429,7 +17415,7 @@
     </x:row>
     <x:row r="215" spans="1:22">
       <x:c r="A215" s="3" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B215" s="3" t="s">
         <x:v>334</x:v>
@@ -17497,7 +17483,7 @@
     </x:row>
     <x:row r="216" spans="1:22">
       <x:c r="A216" s="3" t="s">
-        <x:v>554</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B216" s="3" t="s">
         <x:v>313</x:v>
@@ -17565,7 +17551,7 @@
     </x:row>
     <x:row r="217" spans="1:22">
       <x:c r="A217" s="3" t="s">
-        <x:v>555</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B217" s="3" t="s">
         <x:v>150</x:v>
@@ -17633,7 +17619,7 @@
     </x:row>
     <x:row r="218" spans="1:22">
       <x:c r="A218" s="3" t="s">
-        <x:v>556</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B218" s="3" t="s">
         <x:v>277</x:v>
@@ -17701,7 +17687,7 @@
     </x:row>
     <x:row r="219" spans="1:22">
       <x:c r="A219" s="3" t="s">
-        <x:v>557</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B219" s="3" t="s">
         <x:v>266</x:v>
@@ -17769,7 +17755,7 @@
     </x:row>
     <x:row r="220" spans="1:22">
       <x:c r="A220" s="3" t="s">
-        <x:v>558</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B220" s="3" t="s">
         <x:v>103</x:v>
@@ -17837,7 +17823,7 @@
     </x:row>
     <x:row r="221" spans="1:22">
       <x:c r="A221" s="3" t="s">
-        <x:v>559</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B221" s="3" t="s">
         <x:v>40</x:v>
@@ -17905,7 +17891,7 @@
     </x:row>
     <x:row r="222" spans="1:22">
       <x:c r="A222" s="3" t="s">
-        <x:v>560</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B222" s="3" t="s">
         <x:v>127</x:v>
@@ -17973,7 +17959,7 @@
     </x:row>
     <x:row r="223" spans="1:22">
       <x:c r="A223" s="3" t="s">
-        <x:v>561</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B223" s="3" t="s">
         <x:v>138</x:v>
@@ -18041,7 +18027,7 @@
     </x:row>
     <x:row r="224" spans="1:22">
       <x:c r="A224" s="3" t="s">
-        <x:v>562</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B224" s="3" t="s">
         <x:v>91</x:v>
@@ -18109,7 +18095,7 @@
     </x:row>
     <x:row r="225" spans="1:22">
       <x:c r="A225" s="3" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B225" s="3" t="s">
         <x:v>123</x:v>
@@ -18177,7 +18163,7 @@
     </x:row>
     <x:row r="226" spans="1:22">
       <x:c r="A226" s="3" t="s">
-        <x:v>564</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B226" s="3" t="s">
         <x:v>200</x:v>
@@ -18245,7 +18231,7 @@
     </x:row>
     <x:row r="227" spans="1:22">
       <x:c r="A227" s="3" t="s">
-        <x:v>565</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B227" s="3" t="s">
         <x:v>107</x:v>
@@ -18313,7 +18299,7 @@
     </x:row>
     <x:row r="228" spans="1:22">
       <x:c r="A228" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B228" s="3" t="s">
         <x:v>138</x:v>
@@ -18381,7 +18367,7 @@
     </x:row>
     <x:row r="229" spans="1:22">
       <x:c r="A229" s="3" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B229" s="3" t="s">
         <x:v>226</x:v>
@@ -18449,7 +18435,7 @@
     </x:row>
     <x:row r="230" spans="1:22">
       <x:c r="A230" s="3" t="s">
-        <x:v>568</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B230" s="3" t="s">
         <x:v>296</x:v>
@@ -18517,7 +18503,7 @@
     </x:row>
     <x:row r="231" spans="1:22">
       <x:c r="A231" s="3" t="s">
-        <x:v>569</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B231" s="3" t="s">
         <x:v>81</x:v>
@@ -18585,7 +18571,7 @@
     </x:row>
     <x:row r="232" spans="1:22">
       <x:c r="A232" s="3" t="s">
-        <x:v>570</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B232" s="3" t="s">
         <x:v>23</x:v>
@@ -18653,7 +18639,7 @@
     </x:row>
     <x:row r="233" spans="1:22">
       <x:c r="A233" s="3" t="s">
-        <x:v>571</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B233" s="3" t="s">
         <x:v>292</x:v>
@@ -18721,7 +18707,7 @@
     </x:row>
     <x:row r="234" spans="1:22">
       <x:c r="A234" s="3" t="s">
-        <x:v>572</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B234" s="3" t="s">
         <x:v>99</x:v>
@@ -18789,7 +18775,7 @@
     </x:row>
     <x:row r="235" spans="1:22">
       <x:c r="A235" s="3" t="s">
-        <x:v>573</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B235" s="3" t="s">
         <x:v>259</x:v>
@@ -18857,7 +18843,7 @@
     </x:row>
     <x:row r="236" spans="1:22">
       <x:c r="A236" s="3" t="s">
-        <x:v>574</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B236" s="3" t="s">
         <x:v>83</x:v>
@@ -18925,7 +18911,7 @@
     </x:row>
     <x:row r="237" spans="1:22">
       <x:c r="A237" s="3" t="s">
-        <x:v>575</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B237" s="3" t="s">
         <x:v>245</x:v>
@@ -18993,7 +18979,7 @@
     </x:row>
     <x:row r="238" spans="1:22">
       <x:c r="A238" s="3" t="s">
-        <x:v>576</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B238" s="3" t="s">
         <x:v>169</x:v>
@@ -19061,7 +19047,7 @@
     </x:row>
     <x:row r="239" spans="1:22">
       <x:c r="A239" s="3" t="s">
-        <x:v>577</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B239" s="3" t="s">
         <x:v>77</x:v>
@@ -19129,7 +19115,7 @@
     </x:row>
     <x:row r="240" spans="1:22">
       <x:c r="A240" s="3" t="s">
-        <x:v>578</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B240" s="3" t="s">
         <x:v>229</x:v>
@@ -19197,7 +19183,7 @@
     </x:row>
     <x:row r="241" spans="1:22">
       <x:c r="A241" s="3" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B241" s="3" t="s">
         <x:v>131</x:v>
@@ -19265,7 +19251,7 @@
     </x:row>
     <x:row r="242" spans="1:22">
       <x:c r="A242" s="3" t="s">
-        <x:v>580</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B242" s="3" t="s">
         <x:v>142</x:v>
@@ -19333,7 +19319,7 @@
     </x:row>
     <x:row r="243" spans="1:22">
       <x:c r="A243" s="3" t="s">
-        <x:v>581</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B243" s="3" t="s">
         <x:v>81</x:v>
@@ -19401,7 +19387,7 @@
     </x:row>
     <x:row r="244" spans="1:22">
       <x:c r="A244" s="3" t="s">
-        <x:v>582</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B244" s="3" t="s">
         <x:v>34</x:v>
@@ -19469,7 +19455,7 @@
     </x:row>
     <x:row r="245" spans="1:22">
       <x:c r="A245" s="3" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B245" s="3" t="s">
         <x:v>84</x:v>
@@ -19537,7 +19523,7 @@
     </x:row>
     <x:row r="246" spans="1:22">
       <x:c r="A246" s="3" t="s">
-        <x:v>584</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B246" s="3" t="s">
         <x:v>69</x:v>
@@ -19605,7 +19591,7 @@
     </x:row>
     <x:row r="247" spans="1:22">
       <x:c r="A247" s="3" t="s">
-        <x:v>585</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B247" s="3" t="s">
         <x:v>296</x:v>
@@ -19673,7 +19659,7 @@
     </x:row>
     <x:row r="248" spans="1:22">
       <x:c r="A248" s="3" t="s">
-        <x:v>586</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B248" s="3" t="s">
         <x:v>68</x:v>
@@ -19741,7 +19727,7 @@
     </x:row>
     <x:row r="249" spans="1:22">
       <x:c r="A249" s="3" t="s">
-        <x:v>587</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B249" s="3" t="s">
         <x:v>201</x:v>
@@ -19809,7 +19795,7 @@
     </x:row>
     <x:row r="250" spans="1:22">
       <x:c r="A250" s="3" t="s">
-        <x:v>588</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B250" s="3" t="s">
         <x:v>169</x:v>
@@ -19877,7 +19863,7 @@
     </x:row>
     <x:row r="251" spans="1:22">
       <x:c r="A251" s="3" t="s">
-        <x:v>589</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B251" s="3" t="s">
         <x:v>332</x:v>
@@ -19945,7 +19931,7 @@
     </x:row>
     <x:row r="252" spans="1:22">
       <x:c r="A252" s="3" t="s">
-        <x:v>590</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B252" s="3" t="s">
         <x:v>223</x:v>
@@ -20013,7 +19999,7 @@
     </x:row>
     <x:row r="253" spans="1:22">
       <x:c r="A253" s="3" t="s">
-        <x:v>591</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B253" s="3" t="s">
         <x:v>299</x:v>
@@ -20081,7 +20067,7 @@
     </x:row>
     <x:row r="254" spans="1:22">
       <x:c r="A254" s="3" t="s">
-        <x:v>592</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B254" s="3" t="s">
         <x:v>89</x:v>
@@ -20149,7 +20135,7 @@
     </x:row>
     <x:row r="255" spans="1:22">
       <x:c r="A255" s="3" t="s">
-        <x:v>593</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B255" s="3" t="s">
         <x:v>156</x:v>
@@ -20217,7 +20203,7 @@
     </x:row>
     <x:row r="256" spans="1:22">
       <x:c r="A256" s="3" t="s">
-        <x:v>594</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B256" s="3" t="s">
         <x:v>28</x:v>
@@ -20285,7 +20271,7 @@
     </x:row>
     <x:row r="257" spans="1:22">
       <x:c r="A257" s="3" t="s">
-        <x:v>595</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B257" s="3" t="s">
         <x:v>125</x:v>
@@ -20353,7 +20339,7 @@
     </x:row>
     <x:row r="258" spans="1:22">
       <x:c r="A258" s="3" t="s">
-        <x:v>596</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B258" s="3" t="s">
         <x:v>273</x:v>
@@ -20421,7 +20407,7 @@
     </x:row>
     <x:row r="259" spans="1:22">
       <x:c r="A259" s="3" t="s">
-        <x:v>597</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B259" s="3" t="s">
         <x:v>201</x:v>
@@ -20489,7 +20475,7 @@
     </x:row>
     <x:row r="260" spans="1:22">
       <x:c r="A260" s="3" t="s">
-        <x:v>598</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B260" s="3" t="s">
         <x:v>233</x:v>
@@ -20557,7 +20543,7 @@
     </x:row>
     <x:row r="261" spans="1:22">
       <x:c r="A261" s="3" t="s">
-        <x:v>599</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B261" s="3" t="s">
         <x:v>245</x:v>
@@ -20625,7 +20611,7 @@
     </x:row>
     <x:row r="262" spans="1:22">
       <x:c r="A262" s="3" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B262" s="3" t="s">
         <x:v>48</x:v>
@@ -20693,7 +20679,7 @@
     </x:row>
     <x:row r="263" spans="1:22">
       <x:c r="A263" s="3" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B263" s="3" t="s">
         <x:v>180</x:v>
@@ -20761,7 +20747,7 @@
     </x:row>
     <x:row r="264" spans="1:22">
       <x:c r="A264" s="3" t="s">
-        <x:v>602</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B264" s="3" t="s">
         <x:v>23</x:v>
@@ -20829,7 +20815,7 @@
     </x:row>
     <x:row r="265" spans="1:22">
       <x:c r="A265" s="3" t="s">
-        <x:v>603</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B265" s="3" t="s">
         <x:v>118</x:v>
@@ -20897,7 +20883,7 @@
     </x:row>
     <x:row r="266" spans="1:22">
       <x:c r="A266" s="3" t="s">
-        <x:v>604</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B266" s="3" t="s">
         <x:v>123</x:v>
@@ -20965,7 +20951,7 @@
     </x:row>
     <x:row r="267" spans="1:22">
       <x:c r="A267" s="3" t="s">
-        <x:v>605</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B267" s="3" t="s">
         <x:v>136</x:v>
@@ -21033,7 +21019,7 @@
     </x:row>
     <x:row r="268" spans="1:22">
       <x:c r="A268" s="3" t="s">
-        <x:v>606</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B268" s="3" t="s">
         <x:v>99</x:v>
@@ -21101,7 +21087,7 @@
     </x:row>
     <x:row r="269" spans="1:22">
       <x:c r="A269" s="3" t="s">
-        <x:v>607</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B269" s="3" t="s">
         <x:v>341</x:v>
@@ -21169,7 +21155,7 @@
     </x:row>
     <x:row r="270" spans="1:22">
       <x:c r="A270" s="3" t="s">
-        <x:v>608</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B270" s="3" t="s">
         <x:v>111</x:v>
@@ -21237,7 +21223,7 @@
     </x:row>
     <x:row r="271" spans="1:22">
       <x:c r="A271" s="3" t="s">
-        <x:v>609</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B271" s="3" t="s">
         <x:v>291</x:v>
@@ -21305,7 +21291,7 @@
     </x:row>
     <x:row r="272" spans="1:22">
       <x:c r="A272" s="3" t="s">
-        <x:v>610</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B272" s="3" t="s">
         <x:v>123</x:v>
@@ -21373,7 +21359,7 @@
     </x:row>
     <x:row r="273" spans="1:22">
       <x:c r="A273" s="3" t="s">
-        <x:v>611</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B273" s="3" t="s">
         <x:v>180</x:v>
@@ -21441,7 +21427,7 @@
     </x:row>
     <x:row r="274" spans="1:22">
       <x:c r="A274" s="3" t="s">
-        <x:v>612</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B274" s="3" t="s">
         <x:v>56</x:v>
@@ -21509,7 +21495,7 @@
     </x:row>
     <x:row r="275" spans="1:22">
       <x:c r="A275" s="3" t="s">
-        <x:v>613</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B275" s="3" t="s">
         <x:v>71</x:v>
@@ -21577,7 +21563,7 @@
     </x:row>
     <x:row r="276" spans="1:22">
       <x:c r="A276" s="3" t="s">
-        <x:v>614</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B276" s="3" t="s">
         <x:v>277</x:v>
@@ -21645,7 +21631,7 @@
     </x:row>
     <x:row r="277" spans="1:22">
       <x:c r="A277" s="3" t="s">
-        <x:v>615</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B277" s="3" t="s">
         <x:v>229</x:v>
@@ -21713,7 +21699,7 @@
     </x:row>
     <x:row r="278" spans="1:22">
       <x:c r="A278" s="3" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B278" s="3" t="s">
         <x:v>299</x:v>
@@ -21781,7 +21767,7 @@
     </x:row>
     <x:row r="279" spans="1:22">
       <x:c r="A279" s="3" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B279" s="3" t="s">
         <x:v>92</x:v>
@@ -21849,7 +21835,7 @@
     </x:row>
     <x:row r="280" spans="1:22">
       <x:c r="A280" s="3" t="s">
-        <x:v>618</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B280" s="3" t="s">
         <x:v>360</x:v>
@@ -21917,7 +21903,7 @@
     </x:row>
     <x:row r="281" spans="1:22">
       <x:c r="A281" s="3" t="s">
-        <x:v>619</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B281" s="3" t="s">
         <x:v>295</x:v>
@@ -21985,7 +21971,7 @@
     </x:row>
     <x:row r="282" spans="1:22">
       <x:c r="A282" s="3" t="s">
-        <x:v>620</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B282" s="3" t="s">
         <x:v>108</x:v>
@@ -22053,7 +22039,7 @@
     </x:row>
     <x:row r="283" spans="1:22">
       <x:c r="A283" s="3" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="B283" s="3" t="s">
         <x:v>343</x:v>
@@ -22121,7 +22107,7 @@
     </x:row>
     <x:row r="284" spans="1:22">
       <x:c r="A284" s="3" t="s">
-        <x:v>622</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="B284" s="3" t="s">
         <x:v>320</x:v>
@@ -22189,7 +22175,7 @@
     </x:row>
     <x:row r="285" spans="1:22">
       <x:c r="A285" s="3" t="s">
-        <x:v>623</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="B285" s="3" t="s">
         <x:v>101</x:v>
@@ -22257,7 +22243,7 @@
     </x:row>
     <x:row r="286" spans="1:22">
       <x:c r="A286" s="3" t="s">
-        <x:v>624</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B286" s="3" t="s">
         <x:v>115</x:v>
@@ -22325,7 +22311,7 @@
     </x:row>
     <x:row r="287" spans="1:22">
       <x:c r="A287" s="3" t="s">
-        <x:v>625</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="B287" s="3" t="s">
         <x:v>28</x:v>
@@ -22393,7 +22379,7 @@
     </x:row>
     <x:row r="288" spans="1:22">
       <x:c r="A288" s="3" t="s">
-        <x:v>626</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="B288" s="3" t="s">
         <x:v>229</x:v>
@@ -22461,7 +22447,7 @@
     </x:row>
     <x:row r="289" spans="1:22">
       <x:c r="A289" s="3" t="s">
-        <x:v>627</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="B289" s="3" t="s">
         <x:v>133</x:v>
@@ -22529,7 +22515,7 @@
     </x:row>
     <x:row r="290" spans="1:22">
       <x:c r="A290" s="3" t="s">
-        <x:v>628</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B290" s="3" t="s">
         <x:v>305</x:v>
@@ -22597,7 +22583,7 @@
     </x:row>
     <x:row r="291" spans="1:22">
       <x:c r="A291" s="3" t="s">
-        <x:v>629</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="B291" s="3" t="s">
         <x:v>300</x:v>
@@ -22665,7 +22651,7 @@
     </x:row>
     <x:row r="292" spans="1:22">
       <x:c r="A292" s="3" t="s">
-        <x:v>630</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="B292" s="3" t="s">
         <x:v>76</x:v>
@@ -22733,7 +22719,7 @@
     </x:row>
     <x:row r="293" spans="1:22">
       <x:c r="A293" s="3" t="s">
-        <x:v>631</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="B293" s="3" t="s">
         <x:v>57</x:v>
@@ -22801,7 +22787,7 @@
     </x:row>
     <x:row r="294" spans="1:22">
       <x:c r="A294" s="3" t="s">
-        <x:v>632</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B294" s="3" t="s">
         <x:v>51</x:v>
@@ -22869,7 +22855,7 @@
     </x:row>
     <x:row r="295" spans="1:22">
       <x:c r="A295" s="3" t="s">
-        <x:v>633</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="B295" s="3" t="s">
         <x:v>167</x:v>
@@ -22937,7 +22923,7 @@
     </x:row>
     <x:row r="296" spans="1:22">
       <x:c r="A296" s="3" t="s">
-        <x:v>634</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="B296" s="3" t="s">
         <x:v>341</x:v>
@@ -23005,7 +22991,7 @@
     </x:row>
     <x:row r="297" spans="1:22">
       <x:c r="A297" s="3" t="s">
-        <x:v>635</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="B297" s="3" t="s">
         <x:v>28</x:v>
@@ -23073,7 +23059,7 @@
     </x:row>
     <x:row r="298" spans="1:22">
       <x:c r="A298" s="3" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B298" s="3" t="s">
         <x:v>81</x:v>
@@ -23141,7 +23127,7 @@
     </x:row>
     <x:row r="299" spans="1:22">
       <x:c r="A299" s="3" t="s">
-        <x:v>637</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B299" s="3" t="s">
         <x:v>174</x:v>
@@ -23209,7 +23195,7 @@
     </x:row>
     <x:row r="300" spans="1:22">
       <x:c r="A300" s="3" t="s">
-        <x:v>638</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="B300" s="3" t="s">
         <x:v>133</x:v>
@@ -23277,7 +23263,7 @@
     </x:row>
     <x:row r="301" spans="1:22">
       <x:c r="A301" s="3" t="s">
-        <x:v>639</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="B301" s="3" t="s">
         <x:v>186</x:v>
@@ -23345,7 +23331,7 @@
     </x:row>
     <x:row r="302" spans="1:22">
       <x:c r="A302" s="3" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B302" s="3" t="s">
         <x:v>121</x:v>
@@ -23413,7 +23399,7 @@
     </x:row>
     <x:row r="303" spans="1:22">
       <x:c r="A303" s="3" t="s">
-        <x:v>641</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B303" s="3" t="s">
         <x:v>427</x:v>
@@ -23481,7 +23467,7 @@
     </x:row>
     <x:row r="304" spans="1:22">
       <x:c r="A304" s="3" t="s">
-        <x:v>642</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="B304" s="3" t="s">
         <x:v>101</x:v>
@@ -23549,7 +23535,7 @@
     </x:row>
     <x:row r="305" spans="1:22">
       <x:c r="A305" s="3" t="s">
-        <x:v>643</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="B305" s="3" t="s">
         <x:v>131</x:v>
@@ -23617,7 +23603,7 @@
     </x:row>
     <x:row r="306" spans="1:22">
       <x:c r="A306" s="3" t="s">
-        <x:v>644</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B306" s="3" t="s">
         <x:v>198</x:v>
@@ -23685,7 +23671,7 @@
     </x:row>
     <x:row r="307" spans="1:22">
       <x:c r="A307" s="3" t="s">
-        <x:v>645</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B307" s="3" t="s">
         <x:v>271</x:v>
@@ -23753,7 +23739,7 @@
     </x:row>
     <x:row r="308" spans="1:22">
       <x:c r="A308" s="3" t="s">
-        <x:v>646</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="B308" s="3" t="s">
         <x:v>195</x:v>
@@ -23821,7 +23807,7 @@
     </x:row>
     <x:row r="309" spans="1:22">
       <x:c r="A309" s="3" t="s">
-        <x:v>647</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="B309" s="3" t="s">
         <x:v>427</x:v>
@@ -23889,7 +23875,7 @@
     </x:row>
     <x:row r="310" spans="1:22">
       <x:c r="A310" s="3" t="s">
-        <x:v>648</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="B310" s="3" t="s">
         <x:v>414</x:v>
@@ -23957,7 +23943,7 @@
     </x:row>
     <x:row r="311" spans="1:22">
       <x:c r="A311" s="3" t="s">
-        <x:v>649</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="B311" s="3" t="s">
         <x:v>178</x:v>
@@ -24025,7 +24011,7 @@
     </x:row>
     <x:row r="312" spans="1:22">
       <x:c r="A312" s="3" t="s">
-        <x:v>650</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="B312" s="3" t="s">
         <x:v>189</x:v>
@@ -24093,7 +24079,7 @@
     </x:row>
     <x:row r="313" spans="1:22">
       <x:c r="A313" s="3" t="s">
-        <x:v>651</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="B313" s="3" t="s">
         <x:v>154</x:v>
@@ -24161,7 +24147,7 @@
     </x:row>
     <x:row r="314" spans="1:22">
       <x:c r="A314" s="3" t="s">
-        <x:v>652</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="B314" s="3" t="s">
         <x:v>201</x:v>
@@ -24229,7 +24215,7 @@
     </x:row>
     <x:row r="315" spans="1:22">
       <x:c r="A315" s="3" t="s">
-        <x:v>653</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B315" s="3" t="s">
         <x:v>272</x:v>
@@ -24297,7 +24283,7 @@
     </x:row>
     <x:row r="316" spans="1:22">
       <x:c r="A316" s="3" t="s">
-        <x:v>654</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B316" s="3" t="s">
         <x:v>398</x:v>
@@ -24365,7 +24351,7 @@
     </x:row>
     <x:row r="317" spans="1:22">
       <x:c r="A317" s="3" t="s">
-        <x:v>655</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="B317" s="3" t="s">
         <x:v>107</x:v>
@@ -24433,7 +24419,7 @@
     </x:row>
     <x:row r="318" spans="1:22">
       <x:c r="A318" s="3" t="s">
-        <x:v>656</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="B318" s="3" t="s">
         <x:v>252</x:v>
@@ -24501,7 +24487,7 @@
     </x:row>
     <x:row r="319" spans="1:22">
       <x:c r="A319" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="B319" s="3" t="s">
         <x:v>54</x:v>
@@ -24569,7 +24555,7 @@
     </x:row>
     <x:row r="320" spans="1:22">
       <x:c r="A320" s="3" t="s">
-        <x:v>658</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B320" s="3" t="s">
         <x:v>35</x:v>
@@ -24637,7 +24623,7 @@
     </x:row>
     <x:row r="321" spans="1:22">
       <x:c r="A321" s="3" t="s">
-        <x:v>659</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="B321" s="3" t="s">
         <x:v>84</x:v>
@@ -24705,7 +24691,7 @@
     </x:row>
     <x:row r="322" spans="1:22">
       <x:c r="A322" s="3" t="s">
-        <x:v>660</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B322" s="3" t="s">
         <x:v>375</x:v>
@@ -24773,7 +24759,7 @@
     </x:row>
     <x:row r="323" spans="1:22">
       <x:c r="A323" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B323" s="3" t="s">
         <x:v>191</x:v>
@@ -24841,7 +24827,7 @@
     </x:row>
     <x:row r="324" spans="1:22">
       <x:c r="A324" s="3" t="s">
-        <x:v>662</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B324" s="3" t="s">
         <x:v>79</x:v>
@@ -24909,7 +24895,7 @@
     </x:row>
     <x:row r="325" spans="1:22">
       <x:c r="A325" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B325" s="3" t="s">
         <x:v>231</x:v>
@@ -24977,7 +24963,7 @@
     </x:row>
     <x:row r="326" spans="1:22">
       <x:c r="A326" s="3" t="s">
-        <x:v>664</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="B326" s="3" t="s">
         <x:v>281</x:v>
@@ -25045,7 +25031,7 @@
     </x:row>
     <x:row r="327" spans="1:22">
       <x:c r="A327" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B327" s="3" t="s">
         <x:v>197</x:v>
@@ -25113,7 +25099,7 @@
     </x:row>
     <x:row r="328" spans="1:22">
       <x:c r="A328" s="3" t="s">
-        <x:v>666</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B328" s="3" t="s">
         <x:v>62</x:v>
@@ -25181,7 +25167,7 @@
     </x:row>
     <x:row r="329" spans="1:22">
       <x:c r="A329" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B329" s="3" t="s">
         <x:v>176</x:v>
@@ -25249,7 +25235,7 @@
     </x:row>
     <x:row r="330" spans="1:22">
       <x:c r="A330" s="3" t="s">
-        <x:v>668</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="B330" s="3" t="s">
         <x:v>261</x:v>
@@ -25317,7 +25303,7 @@
     </x:row>
     <x:row r="331" spans="1:22">
       <x:c r="A331" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B331" s="3" t="s">
         <x:v>317</x:v>
@@ -25385,7 +25371,7 @@
     </x:row>
     <x:row r="332" spans="1:22">
       <x:c r="A332" s="3" t="s">
-        <x:v>670</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B332" s="3" t="s">
         <x:v>176</x:v>
@@ -25453,7 +25439,7 @@
     </x:row>
     <x:row r="333" spans="1:22">
       <x:c r="A333" s="3" t="s">
-        <x:v>671</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B333" s="3" t="s">
         <x:v>201</x:v>
@@ -25521,7 +25507,7 @@
     </x:row>
     <x:row r="334" spans="1:22">
       <x:c r="A334" s="3" t="s">
-        <x:v>672</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="B334" s="3" t="s">
         <x:v>197</x:v>
@@ -25589,7 +25575,7 @@
     </x:row>
     <x:row r="335" spans="1:22">
       <x:c r="A335" s="3" t="s">
-        <x:v>673</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B335" s="3" t="s">
         <x:v>176</x:v>
@@ -25657,7 +25643,7 @@
     </x:row>
     <x:row r="336" spans="1:22">
       <x:c r="A336" s="3" t="s">
-        <x:v>674</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B336" s="3" t="s">
         <x:v>251</x:v>
@@ -25725,7 +25711,7 @@
     </x:row>
     <x:row r="337" spans="1:22">
       <x:c r="A337" s="3" t="s">
-        <x:v>675</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B337" s="3" t="s">
         <x:v>68</x:v>
@@ -25793,7 +25779,7 @@
     </x:row>
     <x:row r="338" spans="1:22">
       <x:c r="A338" s="3" t="s">
-        <x:v>676</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="B338" s="3" t="s">
         <x:v>83</x:v>
@@ -25861,7 +25847,7 @@
     </x:row>
     <x:row r="339" spans="1:22">
       <x:c r="A339" s="3" t="s">
-        <x:v>677</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B339" s="3" t="s">
         <x:v>263</x:v>
@@ -25929,7 +25915,7 @@
     </x:row>
     <x:row r="340" spans="1:22">
       <x:c r="A340" s="3" t="s">
-        <x:v>678</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="B340" s="3" t="s">
         <x:v>154</x:v>
@@ -25997,7 +25983,7 @@
     </x:row>
     <x:row r="341" spans="1:22">
       <x:c r="A341" s="3" t="s">
-        <x:v>679</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B341" s="3" t="s">
         <x:v>263</x:v>
@@ -26065,7 +26051,7 @@
     </x:row>
     <x:row r="342" spans="1:22">
       <x:c r="A342" s="3" t="s">
-        <x:v>680</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="B342" s="3" t="s">
         <x:v>103</x:v>
@@ -26133,7 +26119,7 @@
     </x:row>
     <x:row r="343" spans="1:22">
       <x:c r="A343" s="3" t="s">
-        <x:v>681</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B343" s="3" t="s">
         <x:v>427</x:v>
@@ -26201,7 +26187,7 @@
     </x:row>
     <x:row r="344" spans="1:22">
       <x:c r="A344" s="3" t="s">
-        <x:v>682</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B344" s="3" t="s">
         <x:v>427</x:v>
@@ -26269,7 +26255,7 @@
     </x:row>
     <x:row r="345" spans="1:22">
       <x:c r="A345" s="3" t="s">
-        <x:v>683</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B345" s="3" t="s">
         <x:v>91</x:v>
@@ -26337,7 +26323,7 @@
     </x:row>
     <x:row r="346" spans="1:22">
       <x:c r="A346" s="3" t="s">
-        <x:v>684</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B346" s="3" t="s">
         <x:v>26</x:v>
@@ -26405,7 +26391,7 @@
     </x:row>
     <x:row r="347" spans="1:22">
       <x:c r="A347" s="3" t="s">
-        <x:v>685</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B347" s="3" t="s">
         <x:v>140</x:v>
@@ -26473,7 +26459,7 @@
     </x:row>
     <x:row r="348" spans="1:22">
       <x:c r="A348" s="3" t="s">
-        <x:v>686</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="B348" s="3" t="s">
         <x:v>248</x:v>
@@ -26541,7 +26527,7 @@
     </x:row>
     <x:row r="349" spans="1:22">
       <x:c r="A349" s="3" t="s">
-        <x:v>687</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="B349" s="3" t="s">
         <x:v>26</x:v>
@@ -26609,7 +26595,7 @@
     </x:row>
     <x:row r="350" spans="1:22">
       <x:c r="A350" s="3" t="s">
-        <x:v>688</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="B350" s="3" t="s">
         <x:v>200</x:v>
@@ -26677,7 +26663,7 @@
     </x:row>
     <x:row r="351" spans="1:22">
       <x:c r="A351" s="3" t="s">
-        <x:v>689</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="B351" s="3" t="s">
         <x:v>98</x:v>
@@ -26745,7 +26731,7 @@
     </x:row>
     <x:row r="352" spans="1:22">
       <x:c r="A352" s="3" t="s">
-        <x:v>690</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="B352" s="3" t="s">
         <x:v>295</x:v>
@@ -26813,7 +26799,7 @@
     </x:row>
     <x:row r="353" spans="1:22">
       <x:c r="A353" s="3" t="s">
-        <x:v>691</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="B353" s="3" t="s">
         <x:v>299</x:v>
@@ -26881,7 +26867,7 @@
     </x:row>
     <x:row r="354" spans="1:22">
       <x:c r="A354" s="3" t="s">
-        <x:v>692</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="B354" s="3" t="s">
         <x:v>133</x:v>
@@ -26949,7 +26935,7 @@
     </x:row>
     <x:row r="355" spans="1:22">
       <x:c r="A355" s="3" t="s">
-        <x:v>693</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B355" s="3" t="s">
         <x:v>51</x:v>
@@ -27017,7 +27003,7 @@
     </x:row>
     <x:row r="356" spans="1:22">
       <x:c r="A356" s="3" t="s">
-        <x:v>694</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="B356" s="3" t="s">
         <x:v>152</x:v>
@@ -27085,7 +27071,7 @@
     </x:row>
     <x:row r="357" spans="1:22">
       <x:c r="A357" s="3" t="s">
-        <x:v>695</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="B357" s="3" t="s">
         <x:v>266</x:v>
@@ -27153,7 +27139,7 @@
     </x:row>
     <x:row r="358" spans="1:22">
       <x:c r="A358" s="3" t="s">
-        <x:v>696</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="B358" s="3" t="s">
         <x:v>235</x:v>
@@ -27221,7 +27207,7 @@
     </x:row>
     <x:row r="359" spans="1:22">
       <x:c r="A359" s="3" t="s">
-        <x:v>697</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="B359" s="3" t="s">
         <x:v>86</x:v>
@@ -27289,7 +27275,7 @@
     </x:row>
     <x:row r="360" spans="1:22">
       <x:c r="A360" s="3" t="s">
-        <x:v>698</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="B360" s="3" t="s">
         <x:v>284</x:v>
@@ -27357,7 +27343,7 @@
     </x:row>
     <x:row r="361" spans="1:22">
       <x:c r="A361" s="3" t="s">
-        <x:v>699</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="B361" s="3" t="s">
         <x:v>99</x:v>
@@ -27425,7 +27411,7 @@
     </x:row>
     <x:row r="362" spans="1:22">
       <x:c r="A362" s="3" t="s">
-        <x:v>700</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B362" s="3" t="s">
         <x:v>127</x:v>
@@ -27493,7 +27479,7 @@
     </x:row>
     <x:row r="363" spans="1:22">
       <x:c r="A363" s="3" t="s">
-        <x:v>701</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="B363" s="3" t="s">
         <x:v>389</x:v>
@@ -27561,7 +27547,7 @@
     </x:row>
     <x:row r="364" spans="1:22">
       <x:c r="A364" s="3" t="s">
-        <x:v>702</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="B364" s="3" t="s">
         <x:v>201</x:v>
@@ -27629,7 +27615,7 @@
     </x:row>
     <x:row r="365" spans="1:22">
       <x:c r="A365" s="3" t="s">
-        <x:v>703</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B365" s="3" t="s">
         <x:v>201</x:v>
@@ -27697,7 +27683,7 @@
     </x:row>
     <x:row r="366" spans="1:22">
       <x:c r="A366" s="3" t="s">
-        <x:v>704</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B366" s="3" t="s">
         <x:v>53</x:v>
@@ -27765,7 +27751,7 @@
     </x:row>
     <x:row r="367" spans="1:22">
       <x:c r="A367" s="3" t="s">
-        <x:v>705</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="B367" s="3" t="s">
         <x:v>57</x:v>
@@ -27833,7 +27819,7 @@
     </x:row>
     <x:row r="368" spans="1:22">
       <x:c r="A368" s="3" t="s">
-        <x:v>706</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="B368" s="3" t="s">
         <x:v>45</x:v>
@@ -27901,7 +27887,7 @@
     </x:row>
     <x:row r="369" spans="1:22">
       <x:c r="A369" s="3" t="s">
-        <x:v>707</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B369" s="3" t="s">
         <x:v>189</x:v>
@@ -27969,7 +27955,7 @@
     </x:row>
     <x:row r="370" spans="1:22">
       <x:c r="A370" s="3" t="s">
-        <x:v>708</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="B370" s="3" t="s">
         <x:v>331</x:v>
@@ -28037,7 +28023,7 @@
     </x:row>
     <x:row r="371" spans="1:22">
       <x:c r="A371" s="3" t="s">
-        <x:v>709</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="B371" s="3" t="s">
         <x:v>191</x:v>
@@ -28105,7 +28091,7 @@
     </x:row>
     <x:row r="372" spans="1:22">
       <x:c r="A372" s="3" t="s">
-        <x:v>710</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="B372" s="3" t="s">
         <x:v>98</x:v>
@@ -28173,7 +28159,7 @@
     </x:row>
     <x:row r="373" spans="1:22">
       <x:c r="A373" s="3" t="s">
-        <x:v>711</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B373" s="3" t="s">
         <x:v>191</x:v>
@@ -28241,7 +28227,7 @@
     </x:row>
     <x:row r="374" spans="1:22">
       <x:c r="A374" s="3" t="s">
-        <x:v>712</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="B374" s="3" t="s">
         <x:v>120</x:v>
@@ -28309,7 +28295,7 @@
     </x:row>
     <x:row r="375" spans="1:22">
       <x:c r="A375" s="3" t="s">
-        <x:v>713</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B375" s="3" t="s">
         <x:v>35</x:v>
@@ -28377,7 +28363,7 @@
     </x:row>
     <x:row r="376" spans="1:22">
       <x:c r="A376" s="3" t="s">
-        <x:v>714</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B376" s="3" t="s">
         <x:v>26</x:v>
@@ -28445,7 +28431,7 @@
     </x:row>
     <x:row r="377" spans="1:22">
       <x:c r="A377" s="3" t="s">
-        <x:v>715</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B377" s="3" t="s">
         <x:v>312</x:v>
@@ -28513,7 +28499,7 @@
     </x:row>
     <x:row r="378" spans="1:22">
       <x:c r="A378" s="3" t="s">
-        <x:v>716</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B378" s="3" t="s">
         <x:v>86</x:v>
@@ -28581,7 +28567,7 @@
     </x:row>
     <x:row r="379" spans="1:22">
       <x:c r="A379" s="3" t="s">
-        <x:v>717</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B379" s="3" t="s">
         <x:v>115</x:v>
@@ -28649,7 +28635,7 @@
     </x:row>
     <x:row r="380" spans="1:22">
       <x:c r="A380" s="3" t="s">
-        <x:v>718</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="B380" s="3" t="s">
         <x:v>251</x:v>
@@ -28717,7 +28703,7 @@
     </x:row>
     <x:row r="381" spans="1:22">
       <x:c r="A381" s="3" t="s">
-        <x:v>719</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B381" s="3" t="s">
         <x:v>149</x:v>
@@ -28785,7 +28771,7 @@
     </x:row>
     <x:row r="382" spans="1:22">
       <x:c r="A382" s="3" t="s">
-        <x:v>720</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B382" s="3" t="s">
         <x:v>266</x:v>
@@ -28853,7 +28839,7 @@
     </x:row>
     <x:row r="383" spans="1:22">
       <x:c r="A383" s="3" t="s">
-        <x:v>721</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B383" s="3" t="s">
         <x:v>184</x:v>
@@ -28921,7 +28907,7 @@
     </x:row>
     <x:row r="384" spans="1:22">
       <x:c r="A384" s="3" t="s">
-        <x:v>722</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B384" s="3" t="s">
         <x:v>279</x:v>
@@ -28989,7 +28975,7 @@
     </x:row>
     <x:row r="385" spans="1:22">
       <x:c r="A385" s="3" t="s">
-        <x:v>723</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B385" s="3" t="s">
         <x:v>271</x:v>
@@ -29057,7 +29043,7 @@
     </x:row>
     <x:row r="386" spans="1:22">
       <x:c r="A386" s="3" t="s">
-        <x:v>724</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="B386" s="3" t="s">
         <x:v>127</x:v>
@@ -29125,7 +29111,7 @@
     </x:row>
     <x:row r="387" spans="1:22">
       <x:c r="A387" s="3" t="s">
-        <x:v>725</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B387" s="3" t="s">
         <x:v>65</x:v>
@@ -29193,7 +29179,7 @@
     </x:row>
     <x:row r="388" spans="1:22">
       <x:c r="A388" s="3" t="s">
-        <x:v>726</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B388" s="3" t="s">
         <x:v>398</x:v>
@@ -29261,7 +29247,7 @@
     </x:row>
     <x:row r="389" spans="1:22">
       <x:c r="A389" s="3" t="s">
-        <x:v>727</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B389" s="3" t="s">
         <x:v>212</x:v>
@@ -29329,7 +29315,7 @@
     </x:row>
     <x:row r="390" spans="1:22">
       <x:c r="A390" s="3" t="s">
-        <x:v>728</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B390" s="3" t="s">
         <x:v>95</x:v>
@@ -29397,7 +29383,7 @@
     </x:row>
     <x:row r="391" spans="1:22">
       <x:c r="A391" s="3" t="s">
-        <x:v>729</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B391" s="3" t="s">
         <x:v>261</x:v>
@@ -29465,7 +29451,7 @@
     </x:row>
     <x:row r="392" spans="1:22">
       <x:c r="A392" s="3" t="s">
-        <x:v>730</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="B392" s="3" t="s">
         <x:v>89</x:v>
@@ -29533,7 +29519,7 @@
     </x:row>
     <x:row r="393" spans="1:22">
       <x:c r="A393" s="3" t="s">
-        <x:v>731</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B393" s="3" t="s">
         <x:v>300</x:v>
@@ -29601,7 +29587,7 @@
     </x:row>
     <x:row r="394" spans="1:22">
       <x:c r="A394" s="3" t="s">
-        <x:v>732</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B394" s="3" t="s">
         <x:v>180</x:v>
@@ -29669,7 +29655,7 @@
     </x:row>
     <x:row r="395" spans="1:22">
       <x:c r="A395" s="3" t="s">
-        <x:v>733</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B395" s="3" t="s">
         <x:v>154</x:v>
@@ -29737,7 +29723,7 @@
     </x:row>
     <x:row r="396" spans="1:22">
       <x:c r="A396" s="3" t="s">
-        <x:v>734</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B396" s="3" t="s">
         <x:v>296</x:v>
@@ -29805,7 +29791,7 @@
     </x:row>
     <x:row r="397" spans="1:22">
       <x:c r="A397" s="3" t="s">
-        <x:v>735</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B397" s="3" t="s">
         <x:v>275</x:v>
@@ -29873,7 +29859,7 @@
     </x:row>
     <x:row r="398" spans="1:22">
       <x:c r="A398" s="3" t="s">
-        <x:v>736</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="B398" s="3" t="s">
         <x:v>292</x:v>
@@ -29941,7 +29927,7 @@
     </x:row>
     <x:row r="399" spans="1:22">
       <x:c r="A399" s="3" t="s">
-        <x:v>737</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="B399" s="3" t="s">
         <x:v>292</x:v>
@@ -30009,7 +29995,7 @@
     </x:row>
     <x:row r="400" spans="1:22">
       <x:c r="A400" s="3" t="s">
-        <x:v>738</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B400" s="3" t="s">
         <x:v>84</x:v>
@@ -30077,7 +30063,7 @@
     </x:row>
     <x:row r="401" spans="1:22">
       <x:c r="A401" s="3" t="s">
-        <x:v>739</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B401" s="3" t="s">
         <x:v>180</x:v>
@@ -30145,7 +30131,7 @@
     </x:row>
     <x:row r="402" spans="1:22">
       <x:c r="A402" s="3" t="s">
-        <x:v>740</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B402" s="3" t="s">
         <x:v>264</x:v>
@@ -30213,7 +30199,7 @@
     </x:row>
     <x:row r="403" spans="1:22">
       <x:c r="A403" s="3" t="s">
-        <x:v>741</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B403" s="3" t="s">
         <x:v>89</x:v>
@@ -30281,7 +30267,7 @@
     </x:row>
     <x:row r="404" spans="1:22">
       <x:c r="A404" s="3" t="s">
-        <x:v>742</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B404" s="3" t="s">
         <x:v>323</x:v>
@@ -30349,7 +30335,7 @@
     </x:row>
     <x:row r="405" spans="1:22">
       <x:c r="A405" s="3" t="s">
-        <x:v>743</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B405" s="3" t="s">
         <x:v>300</x:v>
@@ -30417,7 +30403,7 @@
     </x:row>
     <x:row r="406" spans="1:22">
       <x:c r="A406" s="3" t="s">
-        <x:v>744</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B406" s="3" t="s">
         <x:v>69</x:v>
@@ -30485,7 +30471,7 @@
     </x:row>
     <x:row r="407" spans="1:22">
       <x:c r="A407" s="3" t="s">
-        <x:v>745</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B407" s="3" t="s">
         <x:v>269</x:v>
@@ -30553,7 +30539,7 @@
     </x:row>
     <x:row r="408" spans="1:22">
       <x:c r="A408" s="3" t="s">
-        <x:v>746</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B408" s="3" t="s">
         <x:v>229</x:v>
@@ -30621,7 +30607,7 @@
     </x:row>
     <x:row r="409" spans="1:22">
       <x:c r="A409" s="3" t="s">
-        <x:v>747</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="B409" s="3" t="s">
         <x:v>275</x:v>
@@ -30689,7 +30675,7 @@
     </x:row>
     <x:row r="410" spans="1:22">
       <x:c r="A410" s="3" t="s">
-        <x:v>748</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B410" s="3" t="s">
         <x:v>295</x:v>
@@ -30757,7 +30743,7 @@
     </x:row>
     <x:row r="411" spans="1:22">
       <x:c r="A411" s="3" t="s">
-        <x:v>749</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B411" s="3" t="s">
         <x:v>320</x:v>
@@ -30825,7 +30811,7 @@
     </x:row>
     <x:row r="412" spans="1:22">
       <x:c r="A412" s="3" t="s">
-        <x:v>750</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B412" s="3" t="s">
         <x:v>159</x:v>
@@ -30893,7 +30879,7 @@
     </x:row>
     <x:row r="413" spans="1:22">
       <x:c r="A413" s="3" t="s">
-        <x:v>751</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B413" s="3" t="s">
         <x:v>256</x:v>
@@ -30961,7 +30947,7 @@
     </x:row>
     <x:row r="414" spans="1:22">
       <x:c r="A414" s="3" t="s">
-        <x:v>752</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B414" s="3" t="s">
         <x:v>226</x:v>
@@ -31029,7 +31015,7 @@
     </x:row>
     <x:row r="415" spans="1:22">
       <x:c r="A415" s="3" t="s">
-        <x:v>753</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="B415" s="3" t="s">
         <x:v>201</x:v>
@@ -31097,7 +31083,7 @@
     </x:row>
     <x:row r="416" spans="1:22">
       <x:c r="A416" s="3" t="s">
-        <x:v>754</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B416" s="3" t="s">
         <x:v>374</x:v>
@@ -31165,7 +31151,7 @@
     </x:row>
     <x:row r="417" spans="1:22">
       <x:c r="A417" s="3" t="s">
-        <x:v>755</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B417" s="3" t="s">
         <x:v>292</x:v>
@@ -31233,7 +31219,7 @@
     </x:row>
     <x:row r="418" spans="1:22">
       <x:c r="A418" s="3" t="s">
-        <x:v>756</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B418" s="3" t="s">
         <x:v>136</x:v>
@@ -31301,7 +31287,7 @@
     </x:row>
     <x:row r="419" spans="1:22">
       <x:c r="A419" s="3" t="s">
-        <x:v>757</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B419" s="3" t="s">
         <x:v>323</x:v>
@@ -31369,7 +31355,7 @@
     </x:row>
     <x:row r="420" spans="1:22">
       <x:c r="A420" s="3" t="s">
-        <x:v>758</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B420" s="3" t="s">
         <x:v>142</x:v>
@@ -31437,7 +31423,7 @@
     </x:row>
     <x:row r="421" spans="1:22">
       <x:c r="A421" s="3" t="s">
-        <x:v>759</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B421" s="3" t="s">
         <x:v>150</x:v>
@@ -31505,7 +31491,7 @@
     </x:row>
     <x:row r="422" spans="1:22">
       <x:c r="A422" s="3" t="s">
-        <x:v>760</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B422" s="3" t="s">
         <x:v>91</x:v>
@@ -31573,7 +31559,7 @@
     </x:row>
     <x:row r="423" spans="1:22">
       <x:c r="A423" s="3" t="s">
-        <x:v>761</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B423" s="3" t="s">
         <x:v>91</x:v>
@@ -31641,7 +31627,7 @@
     </x:row>
     <x:row r="424" spans="1:22">
       <x:c r="A424" s="3" t="s">
-        <x:v>762</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B424" s="3" t="s">
         <x:v>243</x:v>
@@ -31709,7 +31695,7 @@
     </x:row>
     <x:row r="425" spans="1:22">
       <x:c r="A425" s="3" t="s">
-        <x:v>763</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="B425" s="3" t="s">
         <x:v>165</x:v>
@@ -31777,7 +31763,7 @@
     </x:row>
     <x:row r="426" spans="1:22">
       <x:c r="A426" s="3" t="s">
-        <x:v>764</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B426" s="3" t="s">
         <x:v>281</x:v>
@@ -31845,7 +31831,7 @@
     </x:row>
     <x:row r="427" spans="1:22">
       <x:c r="A427" s="3" t="s">
-        <x:v>765</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B427" s="3" t="s">
         <x:v>300</x:v>
@@ -31913,7 +31899,7 @@
     </x:row>
     <x:row r="428" spans="1:22">
       <x:c r="A428" s="3" t="s">
-        <x:v>766</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B428" s="3" t="s">
         <x:v>177</x:v>
@@ -31981,7 +31967,7 @@
     </x:row>
     <x:row r="429" spans="1:22">
       <x:c r="A429" s="3" t="s">
-        <x:v>767</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B429" s="3" t="s">
         <x:v>201</x:v>
@@ -32049,7 +32035,7 @@
     </x:row>
     <x:row r="430" spans="1:22">
       <x:c r="A430" s="3" t="s">
-        <x:v>768</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B430" s="3" t="s">
         <x:v>198</x:v>
@@ -32117,7 +32103,7 @@
     </x:row>
     <x:row r="431" spans="1:22">
       <x:c r="A431" s="3" t="s">
-        <x:v>769</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B431" s="3" t="s">
         <x:v>229</x:v>
@@ -32185,7 +32171,7 @@
     </x:row>
     <x:row r="432" spans="1:22">
       <x:c r="A432" s="3" t="s">
-        <x:v>770</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B432" s="3" t="s">
         <x:v>65</x:v>
@@ -32253,7 +32239,7 @@
     </x:row>
     <x:row r="433" spans="1:22">
       <x:c r="A433" s="3" t="s">
-        <x:v>771</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B433" s="3" t="s">
         <x:v>118</x:v>
@@ -32321,7 +32307,7 @@
     </x:row>
     <x:row r="434" spans="1:22">
       <x:c r="A434" s="3" t="s">
-        <x:v>772</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B434" s="3" t="s">
         <x:v>56</x:v>
@@ -32389,7 +32375,7 @@
     </x:row>
     <x:row r="435" spans="1:22">
       <x:c r="A435" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B435" s="3" t="s">
         <x:v>226</x:v>
@@ -32457,7 +32443,7 @@
     </x:row>
     <x:row r="436" spans="1:22">
       <x:c r="A436" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B436" s="3" t="s">
         <x:v>125</x:v>
@@ -32525,7 +32511,7 @@
     </x:row>
     <x:row r="437" spans="1:22">
       <x:c r="A437" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B437" s="3" t="s">
         <x:v>94</x:v>
@@ -32593,7 +32579,7 @@
     </x:row>
     <x:row r="438" spans="1:22">
       <x:c r="A438" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B438" s="3" t="s">
         <x:v>159</x:v>
@@ -32661,7 +32647,7 @@
     </x:row>
     <x:row r="439" spans="1:22">
       <x:c r="A439" s="3" t="s">
-        <x:v>777</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B439" s="3" t="s">
         <x:v>334</x:v>
@@ -32729,7 +32715,7 @@
     </x:row>
     <x:row r="440" spans="1:22">
       <x:c r="A440" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B440" s="3" t="s">
         <x:v>62</x:v>
@@ -32797,7 +32783,7 @@
     </x:row>
     <x:row r="441" spans="1:22">
       <x:c r="A441" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="B441" s="3" t="s">
         <x:v>239</x:v>
@@ -32865,7 +32851,7 @@
     </x:row>
     <x:row r="442" spans="1:22">
       <x:c r="A442" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B442" s="3" t="s">
         <x:v>29</x:v>
@@ -32933,7 +32919,7 @@
     </x:row>
     <x:row r="443" spans="1:22">
       <x:c r="A443" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B443" s="3" t="s">
         <x:v>211</x:v>
@@ -33001,7 +32987,7 @@
     </x:row>
     <x:row r="444" spans="1:22">
       <x:c r="A444" s="3" t="s">
-        <x:v>782</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B444" s="3" t="s">
         <x:v>200</x:v>
@@ -33069,7 +33055,7 @@
     </x:row>
     <x:row r="445" spans="1:22">
       <x:c r="A445" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B445" s="3" t="s">
         <x:v>226</x:v>
@@ -33137,7 +33123,7 @@
     </x:row>
     <x:row r="446" spans="1:22">
       <x:c r="A446" s="3" t="s">
-        <x:v>784</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B446" s="3" t="s">
         <x:v>214</x:v>
@@ -33205,7 +33191,7 @@
     </x:row>
     <x:row r="447" spans="1:22">
       <x:c r="A447" s="3" t="s">
-        <x:v>785</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B447" s="3" t="s">
         <x:v>248</x:v>
@@ -33273,7 +33259,7 @@
     </x:row>
     <x:row r="448" spans="1:22">
       <x:c r="A448" s="3" t="s">
-        <x:v>786</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B448" s="3" t="s">
         <x:v>26</x:v>
@@ -33341,7 +33327,7 @@
     </x:row>
     <x:row r="449" spans="1:22">
       <x:c r="A449" s="3" t="s">
-        <x:v>787</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B449" s="3" t="s">
         <x:v>279</x:v>
@@ -33409,7 +33395,7 @@
     </x:row>
     <x:row r="450" spans="1:22">
       <x:c r="A450" s="3" t="s">
-        <x:v>788</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B450" s="3" t="s">
         <x:v>84</x:v>
@@ -33477,7 +33463,7 @@
     </x:row>
     <x:row r="451" spans="1:22">
       <x:c r="A451" s="3" t="s">
-        <x:v>789</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B451" s="3" t="s">
         <x:v>279</x:v>
@@ -33545,7 +33531,7 @@
     </x:row>
     <x:row r="452" spans="1:22">
       <x:c r="A452" s="3" t="s">
-        <x:v>790</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B452" s="3" t="s">
         <x:v>426</x:v>
@@ -33613,7 +33599,7 @@
     </x:row>
     <x:row r="453" spans="1:22">
       <x:c r="A453" s="3" t="s">
-        <x:v>791</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B453" s="3" t="s">
         <x:v>169</x:v>
@@ -33681,7 +33667,7 @@
     </x:row>
     <x:row r="454" spans="1:22">
       <x:c r="A454" s="3" t="s">
-        <x:v>792</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B454" s="3" t="s">
         <x:v>131</x:v>
@@ -33749,7 +33735,7 @@
     </x:row>
     <x:row r="455" spans="1:22">
       <x:c r="A455" s="3" t="s">
-        <x:v>793</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B455" s="3" t="s">
         <x:v>92</x:v>
@@ -33817,7 +33803,7 @@
     </x:row>
     <x:row r="456" spans="1:22">
       <x:c r="A456" s="3" t="s">
-        <x:v>794</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B456" s="3" t="s">
         <x:v>107</x:v>
@@ -33885,7 +33871,7 @@
     </x:row>
     <x:row r="457" spans="1:22">
       <x:c r="A457" s="3" t="s">
-        <x:v>795</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B457" s="3" t="s">
         <x:v>374</x:v>
@@ -33953,7 +33939,7 @@
     </x:row>
     <x:row r="458" spans="1:22">
       <x:c r="A458" s="3" t="s">
-        <x:v>796</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B458" s="3" t="s">
         <x:v>406</x:v>
@@ -33992,22 +33978,22 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="N458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="O458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="P458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="Q458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="R458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="S458" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="T458" s="3" t="s">
         <x:v>41</x:v>
@@ -34019,8 +34005,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="459" spans="1:22">
+      <x:c r="A459" s="3" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="B459" s="3" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C459" s="3" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D459" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E459" s="3" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F459" s="3" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G459" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V459" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V458"/>
+  <x:autoFilter ref="A1:V459"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34042,51 +34096,51 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="5" t="s">
+      <x:c r="A1" s="4" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>795</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:2">
+      <x:c r="A2" s="5" t="s">
+        <x:v>796</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>797</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="s">
+    </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="5" t="s">
         <x:v>798</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2">
-      <x:c r="A2" s="6" t="s">
+      <x:c r="B3" s="6" t="s">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="B2" s="7" t="s">
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="5" t="s">
         <x:v>800</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2">
-      <x:c r="A3" s="6" t="s">
+      <x:c r="B4" s="6">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="5" t="s">
         <x:v>801</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="B5" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2">
+      <x:c r="A6" s="5" t="s">
         <x:v>802</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2">
-      <x:c r="A4" s="6" t="s">
-        <x:v>803</x:v>
-      </x:c>
-      <x:c r="B4" s="7">
-        <x:v>457</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2">
-      <x:c r="A5" s="6" t="s">
-        <x:v>804</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:2">
-      <x:c r="A6" s="6" t="s">
-        <x:v>805</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>796</x:v>
+      <x:c r="B6" s="6" t="s">
+        <x:v>793</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
